--- a/paper_traning_lay0x0/sinais_lay0x0_gestao_2026-08-15.xlsx
+++ b/paper_traning_lay0x0/sinais_lay0x0_gestao_2026-08-15.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/paper_traning_lay0x0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_2B593D9757096C5F5FDB331159DDE0324425EB1C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{832AD385-716D-4B19-84E9-28EE837F8A74}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="11_12F93F925739623B739A3A11595ED87656CD0915" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{164EBEE6-0321-41D7-9B8C-40AA5BDBEAD5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="138">
   <si>
     <t>Data</t>
   </si>
@@ -207,6 +207,246 @@
   </si>
   <si>
     <t>97.2%</t>
+  </si>
+  <si>
+    <t>Accrington</t>
+  </si>
+  <si>
+    <t>Colchester</t>
+  </si>
+  <si>
+    <t>Barnet</t>
+  </si>
+  <si>
+    <t>Salford City</t>
+  </si>
+  <si>
+    <t>Cheltenham</t>
+  </si>
+  <si>
+    <t>Rotherham</t>
+  </si>
+  <si>
+    <t>Chesterfield</t>
+  </si>
+  <si>
+    <t>Fleetwood Town</t>
+  </si>
+  <si>
+    <t>Crawley Town</t>
+  </si>
+  <si>
+    <t>Crewe</t>
+  </si>
+  <si>
+    <t>Gillingham</t>
+  </si>
+  <si>
+    <t>Walsall</t>
+  </si>
+  <si>
+    <t>98.8%</t>
+  </si>
+  <si>
+    <t>Northampton</t>
+  </si>
+  <si>
+    <t>Swindon</t>
+  </si>
+  <si>
+    <t>Tranmere</t>
+  </si>
+  <si>
+    <t>Shrewsbury</t>
+  </si>
+  <si>
+    <t>York City</t>
+  </si>
+  <si>
+    <t>Bristol Rovers</t>
+  </si>
+  <si>
+    <t>SCOTLAND 3</t>
+  </si>
+  <si>
+    <t>Alloa</t>
+  </si>
+  <si>
+    <t>Montrose</t>
+  </si>
+  <si>
+    <t>Hamilton</t>
+  </si>
+  <si>
+    <t>Airdrieonians</t>
+  </si>
+  <si>
+    <t>96.2%</t>
+  </si>
+  <si>
+    <t>Peterhead</t>
+  </si>
+  <si>
+    <t>East Fife</t>
+  </si>
+  <si>
+    <t>SCOTLAND 4</t>
+  </si>
+  <si>
+    <t>Annan</t>
+  </si>
+  <si>
+    <t>Clyde</t>
+  </si>
+  <si>
+    <t>Elgin City FC</t>
+  </si>
+  <si>
+    <t>Kelty Hearts</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>SPAIN 2</t>
+  </si>
+  <si>
+    <t>FC Andorra</t>
+  </si>
+  <si>
+    <t>AD Ceuta FC</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>NETHERLANDS 1</t>
+  </si>
+  <si>
+    <t>FC Utrecht</t>
+  </si>
+  <si>
+    <t>Az Alkmaar</t>
+  </si>
+  <si>
+    <t>95.5%</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>Cadiz</t>
+  </si>
+  <si>
+    <t>Celta Vigo B</t>
+  </si>
+  <si>
+    <t>98.5%</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>SAUDI ARABIA 1</t>
+  </si>
+  <si>
+    <t>Al-Ittihad</t>
+  </si>
+  <si>
+    <t>Al-Kholood Club</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>CHILE 2</t>
+  </si>
+  <si>
+    <t>CSD Rangers</t>
+  </si>
+  <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>BRAZIL 1</t>
+  </si>
+  <si>
+    <t>Fluminense</t>
+  </si>
+  <si>
+    <t>SE Palmeiras</t>
+  </si>
+  <si>
+    <t>Mallorca</t>
+  </si>
+  <si>
+    <t>Valladolid</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>PERU 1</t>
+  </si>
+  <si>
+    <t>CD Los Chankas</t>
+  </si>
+  <si>
+    <t>Melgar</t>
+  </si>
+  <si>
+    <t>96.0%</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>BOLIVIA 1</t>
+  </si>
+  <si>
+    <t>Guabira</t>
+  </si>
+  <si>
+    <t>The Strongest</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>Athletico-PR</t>
+  </si>
+  <si>
+    <t>Red Bull Bragantino</t>
+  </si>
+  <si>
+    <t>ECUADOR 1</t>
+  </si>
+  <si>
+    <t>Guayaquil City</t>
+  </si>
+  <si>
+    <t>Libertad FC</t>
+  </si>
+  <si>
+    <t>93.8%</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>Sao Paulo</t>
+  </si>
+  <si>
+    <t>Coritiba</t>
+  </si>
+  <si>
+    <t>Mushuc Runa</t>
+  </si>
+  <si>
+    <t>Barcelona (Ecu)</t>
   </si>
 </sst>
 </file>
@@ -282,6 +522,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -569,7 +813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -696,7 +940,7 @@
         <v>2</v>
       </c>
       <c r="L3" t="str">
-        <f t="shared" ref="L3:L11" si="0">IF(O3=1,"GREEN", "RED")</f>
+        <f t="shared" ref="L3:L38" si="0">IF(O3=1,"GREEN", "RED")</f>
         <v>GREEN</v>
       </c>
       <c r="N3" t="s">
@@ -1064,6 +1308,1221 @@
       </c>
       <c r="O11">
         <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
+        <v>57</v>
+      </c>
+      <c r="H12">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I12">
+        <v>8.3299999999999999E-2</v>
+      </c>
+      <c r="J12">
+        <v>25</v>
+      </c>
+      <c r="K12">
+        <v>2.27</v>
+      </c>
+      <c r="L12" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="N12" t="s">
+        <v>20</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I13">
+        <v>6.6699999999999995E-2</v>
+      </c>
+      <c r="J13">
+        <v>25</v>
+      </c>
+      <c r="K13">
+        <v>1.79</v>
+      </c>
+      <c r="L13" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="N13" t="s">
+        <v>20</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14">
+        <v>13</v>
+      </c>
+      <c r="G14" t="s">
+        <v>57</v>
+      </c>
+      <c r="H14">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I14">
+        <v>7.6899999999999996E-2</v>
+      </c>
+      <c r="J14">
+        <v>25</v>
+      </c>
+      <c r="K14">
+        <v>2.08</v>
+      </c>
+      <c r="L14" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="N14" t="s">
+        <v>20</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F15">
+        <v>13</v>
+      </c>
+      <c r="G15" t="s">
+        <v>57</v>
+      </c>
+      <c r="H15">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I15">
+        <v>7.6899999999999996E-2</v>
+      </c>
+      <c r="J15">
+        <v>25</v>
+      </c>
+      <c r="K15">
+        <v>2.08</v>
+      </c>
+      <c r="L15" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="N15" t="s">
+        <v>20</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16">
+        <v>14</v>
+      </c>
+      <c r="G16" t="s">
+        <v>34</v>
+      </c>
+      <c r="H16">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I16">
+        <v>7.1400000000000005E-2</v>
+      </c>
+      <c r="J16">
+        <v>25</v>
+      </c>
+      <c r="K16">
+        <v>1.92</v>
+      </c>
+      <c r="L16" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="N16" t="s">
+        <v>20</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17">
+        <v>11.5</v>
+      </c>
+      <c r="G17" t="s">
+        <v>70</v>
+      </c>
+      <c r="H17">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I17">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="J17">
+        <v>25</v>
+      </c>
+      <c r="K17">
+        <v>2.38</v>
+      </c>
+      <c r="L17" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="N17" t="s">
+        <v>20</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18">
+        <v>14.5</v>
+      </c>
+      <c r="G18" t="s">
+        <v>46</v>
+      </c>
+      <c r="H18">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I18">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="J18">
+        <v>25</v>
+      </c>
+      <c r="K18">
+        <v>1.85</v>
+      </c>
+      <c r="L18" t="str">
+        <f t="shared" si="0"/>
+        <v>RED</v>
+      </c>
+      <c r="N18" t="s">
+        <v>20</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" t="s">
+        <v>74</v>
+      </c>
+      <c r="F19">
+        <v>11.5</v>
+      </c>
+      <c r="G19" t="s">
+        <v>46</v>
+      </c>
+      <c r="H19">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I19">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="J19">
+        <v>25</v>
+      </c>
+      <c r="K19">
+        <v>2.38</v>
+      </c>
+      <c r="L19" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="N19" t="s">
+        <v>20</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" t="s">
+        <v>76</v>
+      </c>
+      <c r="F20">
+        <v>13</v>
+      </c>
+      <c r="G20" t="s">
+        <v>46</v>
+      </c>
+      <c r="H20">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I20">
+        <v>7.6899999999999996E-2</v>
+      </c>
+      <c r="J20">
+        <v>25</v>
+      </c>
+      <c r="K20">
+        <v>2.08</v>
+      </c>
+      <c r="L20" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="N20" t="s">
+        <v>20</v>
+      </c>
+      <c r="O20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" t="s">
+        <v>79</v>
+      </c>
+      <c r="F21">
+        <v>16.5</v>
+      </c>
+      <c r="G21" t="s">
+        <v>52</v>
+      </c>
+      <c r="H21">
+        <v>0.05</v>
+      </c>
+      <c r="I21">
+        <v>6.0600000000000001E-2</v>
+      </c>
+      <c r="J21">
+        <v>25</v>
+      </c>
+      <c r="K21">
+        <v>1.61</v>
+      </c>
+      <c r="L21" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="N21" t="s">
+        <v>20</v>
+      </c>
+      <c r="O21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" t="s">
+        <v>81</v>
+      </c>
+      <c r="F22">
+        <v>14</v>
+      </c>
+      <c r="G22" t="s">
+        <v>82</v>
+      </c>
+      <c r="H22">
+        <v>0.05</v>
+      </c>
+      <c r="I22">
+        <v>7.1400000000000005E-2</v>
+      </c>
+      <c r="J22">
+        <v>25</v>
+      </c>
+      <c r="K22">
+        <v>1.92</v>
+      </c>
+      <c r="L22" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="N22" t="s">
+        <v>20</v>
+      </c>
+      <c r="O22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" t="s">
+        <v>84</v>
+      </c>
+      <c r="F23">
+        <v>16.5</v>
+      </c>
+      <c r="G23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23">
+        <v>0.05</v>
+      </c>
+      <c r="I23">
+        <v>6.0600000000000001E-2</v>
+      </c>
+      <c r="J23">
+        <v>25</v>
+      </c>
+      <c r="K23">
+        <v>1.61</v>
+      </c>
+      <c r="L23" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="N23" t="s">
+        <v>20</v>
+      </c>
+      <c r="O23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24" t="s">
+        <v>87</v>
+      </c>
+      <c r="F24">
+        <v>19.5</v>
+      </c>
+      <c r="G24" t="s">
+        <v>82</v>
+      </c>
+      <c r="H24">
+        <v>0.06</v>
+      </c>
+      <c r="I24">
+        <v>5.1299999999999998E-2</v>
+      </c>
+      <c r="J24">
+        <v>25</v>
+      </c>
+      <c r="K24">
+        <v>1.35</v>
+      </c>
+      <c r="L24" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="N24" t="s">
+        <v>20</v>
+      </c>
+      <c r="O24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" t="s">
+        <v>85</v>
+      </c>
+      <c r="D25" t="s">
+        <v>88</v>
+      </c>
+      <c r="E25" t="s">
+        <v>89</v>
+      </c>
+      <c r="F25">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>52</v>
+      </c>
+      <c r="H25">
+        <v>0.06</v>
+      </c>
+      <c r="I25">
+        <v>5.5599999999999997E-2</v>
+      </c>
+      <c r="J25">
+        <v>25</v>
+      </c>
+      <c r="K25">
+        <v>1.47</v>
+      </c>
+      <c r="L25" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="N25" t="s">
+        <v>20</v>
+      </c>
+      <c r="O25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" t="s">
+        <v>91</v>
+      </c>
+      <c r="D26" t="s">
+        <v>92</v>
+      </c>
+      <c r="E26" t="s">
+        <v>93</v>
+      </c>
+      <c r="F26">
+        <v>16</v>
+      </c>
+      <c r="G26" t="s">
+        <v>34</v>
+      </c>
+      <c r="H26">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I26">
+        <v>6.25E-2</v>
+      </c>
+      <c r="J26">
+        <v>25</v>
+      </c>
+      <c r="K26">
+        <v>1.67</v>
+      </c>
+      <c r="L26" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="N26" t="s">
+        <v>20</v>
+      </c>
+      <c r="O26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27" t="s">
+        <v>95</v>
+      </c>
+      <c r="D27" t="s">
+        <v>96</v>
+      </c>
+      <c r="E27" t="s">
+        <v>97</v>
+      </c>
+      <c r="F27">
+        <v>19</v>
+      </c>
+      <c r="G27" t="s">
+        <v>98</v>
+      </c>
+      <c r="H27">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I27">
+        <v>5.2600000000000001E-2</v>
+      </c>
+      <c r="J27">
+        <v>25</v>
+      </c>
+      <c r="K27">
+        <v>1.39</v>
+      </c>
+      <c r="L27" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="N27" t="s">
+        <v>20</v>
+      </c>
+      <c r="O27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" t="s">
+        <v>99</v>
+      </c>
+      <c r="C28" t="s">
+        <v>91</v>
+      </c>
+      <c r="D28" t="s">
+        <v>100</v>
+      </c>
+      <c r="E28" t="s">
+        <v>101</v>
+      </c>
+      <c r="F28">
+        <v>14.5</v>
+      </c>
+      <c r="G28" t="s">
+        <v>102</v>
+      </c>
+      <c r="H28">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I28">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="J28">
+        <v>25</v>
+      </c>
+      <c r="K28">
+        <v>1.85</v>
+      </c>
+      <c r="L28" t="str">
+        <f t="shared" si="0"/>
+        <v>RED</v>
+      </c>
+      <c r="N28" t="s">
+        <v>20</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" t="s">
+        <v>104</v>
+      </c>
+      <c r="D29" t="s">
+        <v>105</v>
+      </c>
+      <c r="E29" t="s">
+        <v>106</v>
+      </c>
+      <c r="F29">
+        <v>19.5</v>
+      </c>
+      <c r="G29" t="s">
+        <v>46</v>
+      </c>
+      <c r="H29">
+        <v>0.04</v>
+      </c>
+      <c r="I29">
+        <v>5.1299999999999998E-2</v>
+      </c>
+      <c r="J29">
+        <v>25</v>
+      </c>
+      <c r="K29">
+        <v>1.35</v>
+      </c>
+      <c r="L29" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="N29" t="s">
+        <v>20</v>
+      </c>
+      <c r="O29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" t="s">
+        <v>107</v>
+      </c>
+      <c r="C30" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" t="s">
+        <v>109</v>
+      </c>
+      <c r="E30" t="s">
+        <v>110</v>
+      </c>
+      <c r="F30">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30">
+        <v>0.05</v>
+      </c>
+      <c r="I30">
+        <v>5.5599999999999997E-2</v>
+      </c>
+      <c r="J30">
+        <v>25</v>
+      </c>
+      <c r="K30">
+        <v>1.47</v>
+      </c>
+      <c r="L30" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="N30" t="s">
+        <v>20</v>
+      </c>
+      <c r="O30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" t="s">
+        <v>111</v>
+      </c>
+      <c r="C31" t="s">
+        <v>112</v>
+      </c>
+      <c r="D31" t="s">
+        <v>113</v>
+      </c>
+      <c r="E31" t="s">
+        <v>114</v>
+      </c>
+      <c r="F31">
+        <v>10.5</v>
+      </c>
+      <c r="G31" t="s">
+        <v>29</v>
+      </c>
+      <c r="H31">
+        <v>0.05</v>
+      </c>
+      <c r="I31">
+        <v>9.5200000000000007E-2</v>
+      </c>
+      <c r="J31">
+        <v>25</v>
+      </c>
+      <c r="K31">
+        <v>2.63</v>
+      </c>
+      <c r="L31" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="N31" t="s">
+        <v>20</v>
+      </c>
+      <c r="O31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" t="s">
+        <v>111</v>
+      </c>
+      <c r="C32" t="s">
+        <v>91</v>
+      </c>
+      <c r="D32" t="s">
+        <v>115</v>
+      </c>
+      <c r="E32" t="s">
+        <v>116</v>
+      </c>
+      <c r="F32">
+        <v>14</v>
+      </c>
+      <c r="G32" t="s">
+        <v>46</v>
+      </c>
+      <c r="H32">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I32">
+        <v>7.1400000000000005E-2</v>
+      </c>
+      <c r="J32">
+        <v>25</v>
+      </c>
+      <c r="K32">
+        <v>1.92</v>
+      </c>
+      <c r="L32" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="N32" t="s">
+        <v>20</v>
+      </c>
+      <c r="O32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" t="s">
+        <v>117</v>
+      </c>
+      <c r="C33" t="s">
+        <v>118</v>
+      </c>
+      <c r="D33" t="s">
+        <v>119</v>
+      </c>
+      <c r="E33" t="s">
+        <v>120</v>
+      </c>
+      <c r="F33">
+        <v>16</v>
+      </c>
+      <c r="G33" t="s">
+        <v>121</v>
+      </c>
+      <c r="H33">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I33">
+        <v>6.25E-2</v>
+      </c>
+      <c r="J33">
+        <v>25</v>
+      </c>
+      <c r="K33">
+        <v>1.67</v>
+      </c>
+      <c r="L33" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="N33" t="s">
+        <v>20</v>
+      </c>
+      <c r="O33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" t="s">
+        <v>122</v>
+      </c>
+      <c r="C34" t="s">
+        <v>123</v>
+      </c>
+      <c r="D34" t="s">
+        <v>124</v>
+      </c>
+      <c r="E34" t="s">
+        <v>125</v>
+      </c>
+      <c r="F34">
+        <v>20</v>
+      </c>
+      <c r="G34" t="s">
+        <v>102</v>
+      </c>
+      <c r="H34">
+        <v>0.06</v>
+      </c>
+      <c r="I34">
+        <v>0.05</v>
+      </c>
+      <c r="J34">
+        <v>25</v>
+      </c>
+      <c r="K34">
+        <v>1.32</v>
+      </c>
+      <c r="L34" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="N34" t="s">
+        <v>20</v>
+      </c>
+      <c r="O34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" t="s">
+        <v>126</v>
+      </c>
+      <c r="C35" t="s">
+        <v>112</v>
+      </c>
+      <c r="D35" t="s">
+        <v>127</v>
+      </c>
+      <c r="E35" t="s">
+        <v>128</v>
+      </c>
+      <c r="F35">
+        <v>11</v>
+      </c>
+      <c r="G35" t="s">
+        <v>102</v>
+      </c>
+      <c r="H35">
+        <v>0.05</v>
+      </c>
+      <c r="I35">
+        <v>9.0899999999999995E-2</v>
+      </c>
+      <c r="J35">
+        <v>25</v>
+      </c>
+      <c r="K35">
+        <v>2.5</v>
+      </c>
+      <c r="L35" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="N35" t="s">
+        <v>20</v>
+      </c>
+      <c r="O35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" t="s">
+        <v>126</v>
+      </c>
+      <c r="C36" t="s">
+        <v>129</v>
+      </c>
+      <c r="D36" t="s">
+        <v>130</v>
+      </c>
+      <c r="E36" t="s">
+        <v>131</v>
+      </c>
+      <c r="F36">
+        <v>14.5</v>
+      </c>
+      <c r="G36" t="s">
+        <v>132</v>
+      </c>
+      <c r="H36">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I36">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="J36">
+        <v>14.24</v>
+      </c>
+      <c r="K36">
+        <v>1.05</v>
+      </c>
+      <c r="L36" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="N36" t="s">
+        <v>20</v>
+      </c>
+      <c r="O36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37" t="s">
+        <v>133</v>
+      </c>
+      <c r="C37" t="s">
+        <v>112</v>
+      </c>
+      <c r="D37" t="s">
+        <v>134</v>
+      </c>
+      <c r="E37" t="s">
+        <v>135</v>
+      </c>
+      <c r="F37">
+        <v>12.5</v>
+      </c>
+      <c r="G37" t="s">
+        <v>102</v>
+      </c>
+      <c r="H37">
+        <v>0.05</v>
+      </c>
+      <c r="I37">
+        <v>0.08</v>
+      </c>
+      <c r="J37">
+        <v>25</v>
+      </c>
+      <c r="K37">
+        <v>2.17</v>
+      </c>
+      <c r="L37" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="N37" t="s">
+        <v>20</v>
+      </c>
+      <c r="O37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>14</v>
+      </c>
+      <c r="B38" t="s">
+        <v>133</v>
+      </c>
+      <c r="C38" t="s">
+        <v>129</v>
+      </c>
+      <c r="D38" t="s">
+        <v>136</v>
+      </c>
+      <c r="E38" t="s">
+        <v>137</v>
+      </c>
+      <c r="F38">
+        <v>13.5</v>
+      </c>
+      <c r="G38" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I38">
+        <v>7.4099999999999999E-2</v>
+      </c>
+      <c r="J38">
+        <v>25</v>
+      </c>
+      <c r="K38">
+        <v>2</v>
+      </c>
+      <c r="L38" t="str">
+        <f t="shared" si="0"/>
+        <v>RED</v>
+      </c>
+      <c r="N38" t="s">
+        <v>20</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
